--- a/risk/Risk_Analysis_T3_500yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_500yrs_Future_Breaches.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>465.75</v>
+        <v>17887.23</v>
       </c>
       <c r="C4" t="n">
-        <v>166824</v>
+        <v>4121712</v>
       </c>
       <c r="D4" t="n">
-        <v>131076</v>
+        <v>3238488</v>
       </c>
       <c r="E4" t="n">
-        <v>69300</v>
+        <v>1396800</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>1650</v>
+        <v>55920</v>
       </c>
       <c r="H4" t="n">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5130</v>
+        <v>133800</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1418.04</v>
+        <v>21599.73</v>
       </c>
       <c r="C5" t="n">
-        <v>307944</v>
+        <v>4032000</v>
       </c>
       <c r="D5" t="n">
-        <v>241956</v>
+        <v>3168000</v>
       </c>
       <c r="E5" t="n">
-        <v>67500</v>
+        <v>1298700</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>4260</v>
+        <v>58080</v>
       </c>
       <c r="H5" t="n">
-        <v>1890</v>
+        <v>3630</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>11550</v>
+        <v>132900</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2486.7</v>
+        <v>19456.74</v>
       </c>
       <c r="C6" t="n">
-        <v>520632</v>
+        <v>2949408</v>
       </c>
       <c r="D6" t="n">
-        <v>409068</v>
+        <v>2317392</v>
       </c>
       <c r="E6" t="n">
-        <v>117000</v>
+        <v>944100</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>9480</v>
+        <v>68280</v>
       </c>
       <c r="H6" t="n">
-        <v>210</v>
+        <v>7260</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>20490</v>
+        <v>107580</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>3306.06</v>
+        <v>17623.71</v>
       </c>
       <c r="C7" t="n">
-        <v>655200</v>
+        <v>2805264</v>
       </c>
       <c r="D7" t="n">
-        <v>514800</v>
+        <v>2204136</v>
       </c>
       <c r="E7" t="n">
-        <v>123300</v>
+        <v>803700</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>7440</v>
+        <v>44460</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2430</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>15360</v>
+        <v>102180</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>3595.95</v>
+        <v>16953.03</v>
       </c>
       <c r="C8" t="n">
-        <v>489888</v>
+        <v>3041136</v>
       </c>
       <c r="D8" t="n">
-        <v>384912</v>
+        <v>2389464</v>
       </c>
       <c r="E8" t="n">
-        <v>79200</v>
+        <v>719100</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>6630</v>
+        <v>41460</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4380</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>18300</v>
+        <v>109200</v>
       </c>
     </row>
     <row r="9">
@@ -10033,37 +10027,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>3000.51</v>
+        <v>21833.19</v>
       </c>
       <c r="C9" t="n">
-        <v>271656</v>
+        <v>3519432</v>
       </c>
       <c r="D9" t="n">
-        <v>213444</v>
+        <v>2765268</v>
       </c>
       <c r="E9" t="n">
-        <v>52200</v>
+        <v>778500</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>4020</v>
+        <v>70890</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>10020</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>15870</v>
+        <v>144720</v>
       </c>
     </row>
     <row r="10">
@@ -10071,25 +10065,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>1544.4</v>
+        <v>29727.81</v>
       </c>
       <c r="C10" t="n">
-        <v>110376</v>
+        <v>4277448</v>
       </c>
       <c r="D10" t="n">
-        <v>86724</v>
+        <v>3360852</v>
       </c>
       <c r="E10" t="n">
-        <v>25200</v>
+        <v>838800</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1740</v>
+        <v>79320</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>11910</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9060</v>
+        <v>186630</v>
       </c>
     </row>
     <row r="11">
@@ -10109,37 +10103,37 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>687.6</v>
+        <v>29466.63</v>
       </c>
       <c r="C11" t="n">
-        <v>46368</v>
+        <v>2706480</v>
       </c>
       <c r="D11" t="n">
-        <v>36432</v>
+        <v>2126520</v>
       </c>
       <c r="E11" t="n">
-        <v>21600</v>
+        <v>306900</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1470</v>
+        <v>61140</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1650</v>
+        <v>129630</v>
       </c>
     </row>
     <row r="12">
@@ -10147,37 +10141,37 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>419.4</v>
+        <v>25048.17</v>
       </c>
       <c r="C12" t="n">
-        <v>17136</v>
+        <v>1817928</v>
       </c>
       <c r="D12" t="n">
-        <v>13464</v>
+        <v>1428372</v>
       </c>
       <c r="E12" t="n">
-        <v>2700</v>
+        <v>148500</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>540</v>
+        <v>35100</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>360</v>
+        <v>77010</v>
       </c>
     </row>
     <row r="13">
@@ -10185,22 +10179,22 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>266.4</v>
+        <v>14693.49</v>
       </c>
       <c r="C13" t="n">
-        <v>1512</v>
+        <v>939456</v>
       </c>
       <c r="D13" t="n">
-        <v>1188</v>
+        <v>738144</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>50400</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>210</v>
+        <v>25770</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10209,13 +10203,13 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>450</v>
+        <v>42060</v>
       </c>
     </row>
     <row r="14">
@@ -10223,25 +10217,25 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>150.39</v>
+        <v>1829.43</v>
       </c>
       <c r="C14" t="n">
-        <v>2016</v>
+        <v>116928</v>
       </c>
       <c r="D14" t="n">
-        <v>1584</v>
+        <v>91872</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>540</v>
+        <v>2550</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>810</v>
+        <v>11760</v>
       </c>
     </row>
     <row r="15">
@@ -10261,22 +10255,22 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>112.68</v>
+        <v>374.76</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>53424</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>41976</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>132.75</v>
+        <v>175.68</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>11088</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>8712</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>3.87</v>
+        <v>116.28</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2.34</v>
+        <v>12.96</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
     </row>
     <row r="19">
@@ -10413,13 +10407,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>1.08</v>
+        <v>17.64</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10428,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10443,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20">
@@ -10451,13 +10445,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.09</v>
+        <v>10.62</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10466,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -10481,7 +10475,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="21">
@@ -10489,13 +10483,13 @@
         <v>850</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10504,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -10519,7 +10513,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
     </row>
     <row r="22">
@@ -10527,13 +10521,13 @@
         <v>900</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10542,7 +10536,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -10557,7 +10551,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23">
@@ -10565,13 +10559,13 @@
         <v>950</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10580,7 +10574,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>638.12</v>
+        <v>9719.879999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>169369.2</v>
+        <v>2217600</v>
       </c>
       <c r="D5" t="n">
-        <v>80087.44</v>
+        <v>1048608</v>
       </c>
       <c r="E5" t="n">
-        <v>7445.25</v>
+        <v>143246.61</v>
       </c>
       <c r="F5" t="n">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>680.4</v>
+        <v>1306.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2425.5</v>
+        <v>27909</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>1989.36</v>
+        <v>15565.39</v>
       </c>
       <c r="C6" t="n">
-        <v>468568.8</v>
+        <v>2654467.2</v>
       </c>
       <c r="D6" t="n">
-        <v>207397.48</v>
+        <v>1174917.74</v>
       </c>
       <c r="E6" t="n">
-        <v>19773</v>
+        <v>159552.9</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>474</v>
+        <v>3414</v>
       </c>
       <c r="H6" t="n">
-        <v>119.7</v>
+        <v>4138.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7581.3</v>
+        <v>39804.6</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>3140.76</v>
+        <v>16742.52</v>
       </c>
       <c r="C7" t="n">
-        <v>655200</v>
+        <v>2805264</v>
       </c>
       <c r="D7" t="n">
-        <v>328442.4</v>
+        <v>1406238.77</v>
       </c>
       <c r="E7" t="n">
-        <v>26225.91</v>
+        <v>170946.99</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1116</v>
+        <v>6669</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1773.9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9216</v>
+        <v>61308</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>3595.95</v>
+        <v>16953.03</v>
       </c>
       <c r="C8" t="n">
-        <v>489888</v>
+        <v>3041136</v>
       </c>
       <c r="D8" t="n">
-        <v>283295.23</v>
+        <v>1758645.5</v>
       </c>
       <c r="E8" t="n">
-        <v>19427.76</v>
+        <v>176395.23</v>
       </c>
       <c r="F8" t="n">
-        <v>0.95</v>
+        <v>7.6</v>
       </c>
       <c r="G8" t="n">
-        <v>4309.5</v>
+        <v>26949</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3723</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>12993</v>
+        <v>77532</v>
       </c>
     </row>
     <row r="9">
@@ -11897,37 +11891,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>3000.51</v>
+        <v>21833.19</v>
       </c>
       <c r="C9" t="n">
-        <v>271656</v>
+        <v>3519432</v>
       </c>
       <c r="D9" t="n">
-        <v>171395.53</v>
+        <v>2220510.2</v>
       </c>
       <c r="E9" t="n">
-        <v>13973.94</v>
+        <v>208404.45</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>3417</v>
+        <v>60256.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>10020</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>12854.7</v>
+        <v>117223.2</v>
       </c>
     </row>
     <row r="10">
@@ -11935,25 +11929,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>1544.4</v>
+        <v>29727.81</v>
       </c>
       <c r="C10" t="n">
-        <v>110376</v>
+        <v>4277448</v>
       </c>
       <c r="D10" t="n">
-        <v>75449.88</v>
+        <v>2923941.24</v>
       </c>
       <c r="E10" t="n">
-        <v>7308</v>
+        <v>243252</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1740</v>
+        <v>79320</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>11910</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>8063.4</v>
+        <v>166100.7</v>
       </c>
     </row>
     <row r="11">
@@ -11973,37 +11967,37 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>687.6</v>
+        <v>29466.63</v>
       </c>
       <c r="C11" t="n">
-        <v>46368</v>
+        <v>2706480</v>
       </c>
       <c r="D11" t="n">
-        <v>32734.15</v>
+        <v>1910678.22</v>
       </c>
       <c r="E11" t="n">
-        <v>8851.68</v>
+        <v>125767.62</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1470</v>
+        <v>61140</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1650</v>
+        <v>129630</v>
       </c>
     </row>
     <row r="12">
@@ -12011,37 +12005,37 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>419.4</v>
+        <v>25048.17</v>
       </c>
       <c r="C12" t="n">
-        <v>17136</v>
+        <v>1817928</v>
       </c>
       <c r="D12" t="n">
-        <v>12481.13</v>
+        <v>1324100.84</v>
       </c>
       <c r="E12" t="n">
-        <v>1290.6</v>
+        <v>70983</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>540</v>
+        <v>35100</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>360</v>
+        <v>77010</v>
       </c>
     </row>
     <row r="13">
@@ -12049,22 +12043,22 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>266.4</v>
+        <v>14693.49</v>
       </c>
       <c r="C13" t="n">
-        <v>1512</v>
+        <v>939456</v>
       </c>
       <c r="D13" t="n">
-        <v>1128.01</v>
+        <v>700867.73</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>26671.68</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>210</v>
+        <v>25770</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12073,13 +12067,13 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>450</v>
+        <v>42060</v>
       </c>
     </row>
     <row r="14">
@@ -12087,25 +12081,25 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>150.39</v>
+        <v>1829.43</v>
       </c>
       <c r="C14" t="n">
-        <v>2016</v>
+        <v>116928</v>
       </c>
       <c r="D14" t="n">
-        <v>1539.65</v>
+        <v>89299.58</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>4098.96</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>540</v>
+        <v>2550</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>810</v>
+        <v>11760</v>
       </c>
     </row>
     <row r="15">
@@ -12125,22 +12119,22 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>112.68</v>
+        <v>374.76</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>53424</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>41388.34</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>536.67</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>132.75</v>
+        <v>175.68</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>11088</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>8712</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>3.87</v>
+        <v>116.28</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2.34</v>
+        <v>12.96</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
     </row>
     <row r="19">
@@ -12277,13 +12271,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>1.08</v>
+        <v>17.64</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12307,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20">
@@ -12315,13 +12309,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.09</v>
+        <v>10.62</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12330,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -12345,7 +12339,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="21">
@@ -12353,13 +12347,13 @@
         <v>850</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -12368,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -12383,7 +12377,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
     </row>
     <row r="22">
@@ -12391,13 +12385,13 @@
         <v>900</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12406,7 +12400,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3780</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -12421,7 +12415,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23">
@@ -12429,13 +12423,13 @@
         <v>950</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12444,7 +12438,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1403859.6</v>
+        <v>21383732.7</v>
       </c>
       <c r="C5" t="n">
-        <v>9315306</v>
+        <v>121968000</v>
       </c>
       <c r="D5" t="n">
-        <v>8115259.89</v>
+        <v>106255448.64</v>
       </c>
       <c r="E5" t="n">
-        <v>1371712.86</v>
+        <v>26391755.43</v>
       </c>
       <c r="F5" t="n">
-        <v>5000.04</v>
+        <v>22500.18</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>188232.66</v>
+        <v>361526.22</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>52499.7</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>22848.21</v>
+        <v>262902.78</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>4376592</v>
+        <v>34243862.4</v>
       </c>
       <c r="C6" t="n">
-        <v>25771284</v>
+        <v>145995696</v>
       </c>
       <c r="D6" t="n">
-        <v>21015586.24</v>
+        <v>119054415</v>
       </c>
       <c r="E6" t="n">
-        <v>3642977.52</v>
+        <v>29396026.3</v>
       </c>
       <c r="F6" t="n">
-        <v>29166.9</v>
+        <v>58333.8</v>
       </c>
       <c r="G6" t="n">
-        <v>8769</v>
+        <v>63159</v>
       </c>
       <c r="H6" t="n">
-        <v>33115</v>
+        <v>1144833.03</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>379164.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>71415.85000000001</v>
+        <v>374959.33</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>6909665.4</v>
+        <v>36833553.9</v>
       </c>
       <c r="C7" t="n">
-        <v>36036000</v>
+        <v>154289520</v>
       </c>
       <c r="D7" t="n">
-        <v>33281068.39</v>
+        <v>142494174.36</v>
       </c>
       <c r="E7" t="n">
-        <v>4831861.66</v>
+        <v>31495273.44</v>
       </c>
       <c r="F7" t="n">
-        <v>50000.4</v>
+        <v>275002.2</v>
       </c>
       <c r="G7" t="n">
-        <v>20646</v>
+        <v>123376.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>490749.43</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>163332.4</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>86814.72</v>
+        <v>577521.36</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>7911090</v>
+        <v>37296666</v>
       </c>
       <c r="C8" t="n">
-        <v>26943840</v>
+        <v>167262480</v>
       </c>
       <c r="D8" t="n">
-        <v>28706305.86</v>
+        <v>178203548.92</v>
       </c>
       <c r="E8" t="n">
-        <v>3579370.5</v>
+        <v>32499057.18</v>
       </c>
       <c r="F8" t="n">
-        <v>39583.65</v>
+        <v>316669.2</v>
       </c>
       <c r="G8" t="n">
-        <v>79725.75</v>
+        <v>498556.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1029967.95</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>148749.15</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>122394.06</v>
+        <v>730351.4399999999</v>
       </c>
     </row>
     <row r="9">
@@ -12829,37 +12823,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>6601122</v>
+        <v>48033018</v>
       </c>
       <c r="C9" t="n">
-        <v>14941080</v>
+        <v>193568760</v>
       </c>
       <c r="D9" t="n">
-        <v>17367509.26</v>
+        <v>225004298.97</v>
       </c>
       <c r="E9" t="n">
-        <v>2574558.71</v>
+        <v>38396435.87</v>
       </c>
       <c r="F9" t="n">
-        <v>125001</v>
+        <v>541671</v>
       </c>
       <c r="G9" t="n">
-        <v>63214.5</v>
+        <v>1114745.25</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2772033</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>332498.1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>121091.27</v>
+        <v>1104242.54</v>
       </c>
     </row>
     <row r="10">
@@ -12867,25 +12861,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>3397680</v>
+        <v>65401182</v>
       </c>
       <c r="C10" t="n">
-        <v>6070680</v>
+        <v>235259640</v>
       </c>
       <c r="D10" t="n">
-        <v>7645336.34</v>
+        <v>296282965.85</v>
       </c>
       <c r="E10" t="n">
-        <v>1346425.92</v>
+        <v>44816748.48</v>
       </c>
       <c r="F10" t="n">
-        <v>41667</v>
+        <v>83334</v>
       </c>
       <c r="G10" t="n">
-        <v>32190</v>
+        <v>1467420</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3294901.5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>75957.23</v>
+        <v>1564668.59</v>
       </c>
     </row>
     <row r="11">
@@ -12905,37 +12899,37 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>1512720</v>
+        <v>64826586</v>
       </c>
       <c r="C11" t="n">
-        <v>2550240</v>
+        <v>148856400</v>
       </c>
       <c r="D11" t="n">
-        <v>3316951.62</v>
+        <v>193609024.03</v>
       </c>
       <c r="E11" t="n">
-        <v>1630833.52</v>
+        <v>23171426.31</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>27195</v>
+        <v>1131090</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>248985</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>116666</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>15543</v>
+        <v>1221114.6</v>
       </c>
     </row>
     <row r="12">
@@ -12943,37 +12937,37 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>922680</v>
+        <v>55105974</v>
       </c>
       <c r="C12" t="n">
-        <v>942480</v>
+        <v>99986040</v>
       </c>
       <c r="D12" t="n">
-        <v>1264712.7</v>
+        <v>134171138.52</v>
       </c>
       <c r="E12" t="n">
-        <v>237780.14</v>
+        <v>13077907.92</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>9990</v>
+        <v>649350</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>116666</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3391.2</v>
+        <v>725434.2</v>
       </c>
     </row>
     <row r="13">
@@ -12981,22 +12975,22 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>586080</v>
+        <v>32325678</v>
       </c>
       <c r="C13" t="n">
-        <v>83160</v>
+        <v>51670080</v>
       </c>
       <c r="D13" t="n">
-        <v>114300.85</v>
+        <v>71018926.88</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>4913990.32</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>3885</v>
+        <v>476745</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13005,13 +12999,13 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>58333</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4239</v>
+        <v>396205.2</v>
       </c>
     </row>
     <row r="14">
@@ -13019,25 +13013,25 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>330858</v>
+        <v>4024746</v>
       </c>
       <c r="C14" t="n">
-        <v>110880</v>
+        <v>6431040</v>
       </c>
       <c r="D14" t="n">
-        <v>156012.53</v>
+        <v>9048726.85</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>755192.39</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>9990</v>
+        <v>47175</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>7630.2</v>
+        <v>110779.2</v>
       </c>
     </row>
     <row r="15">
@@ -13057,22 +13051,22 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>247896</v>
+        <v>824472</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2938320</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>4193880.09</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>98876.08</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>24975</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>45498.6</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>292050</v>
+        <v>386496</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>609840</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>882786.96</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>6105</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>28260</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>8514</v>
+        <v>255816</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>120380.04</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4995</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>7912.8</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>5148</v>
+        <v>28512</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>110880</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>160506.72</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2220</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>7630.2</v>
       </c>
     </row>
     <row r="19">
@@ -13209,13 +13203,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>2376</v>
+        <v>38808</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13224,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13239,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="20">
@@ -13247,13 +13241,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>198</v>
+        <v>23364</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13262,7 +13256,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1110</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -13277,7 +13271,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3391.2</v>
       </c>
     </row>
     <row r="21">
@@ -13285,13 +13279,13 @@
         <v>850</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>12276</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13300,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3885</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -13315,7 +13309,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>5934.6</v>
       </c>
     </row>
     <row r="22">
@@ -13323,13 +13317,13 @@
         <v>900</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>3762</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>280886.76</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13338,7 +13332,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>69930</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -13353,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3108.6</v>
       </c>
     </row>
     <row r="23">
@@ -13361,13 +13355,13 @@
         <v>950</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13376,7 +13370,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>280886.76</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>17887.23</v>
+        <v>46396.89</v>
       </c>
       <c r="C4" t="n">
-        <v>4121712</v>
+        <v>6009192</v>
       </c>
       <c r="D4" t="n">
-        <v>3238488</v>
+        <v>4721508</v>
       </c>
       <c r="E4" t="n">
-        <v>1396800</v>
+        <v>1489500</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>55920</v>
+        <v>146730</v>
       </c>
       <c r="H4" t="n">
-        <v>6000</v>
+        <v>23130</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>133800</v>
+        <v>438840</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>21599.73</v>
+        <v>28856.25</v>
       </c>
       <c r="C5" t="n">
-        <v>4032000</v>
+        <v>2060856</v>
       </c>
       <c r="D5" t="n">
-        <v>3168000</v>
+        <v>1619244</v>
       </c>
       <c r="E5" t="n">
-        <v>1298700</v>
+        <v>387900</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>58080</v>
+        <v>71820</v>
       </c>
       <c r="H5" t="n">
-        <v>3630</v>
+        <v>7770</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>132900</v>
+        <v>246420</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>19456.74</v>
+        <v>3832.65</v>
       </c>
       <c r="C6" t="n">
-        <v>2949408</v>
+        <v>224784</v>
       </c>
       <c r="D6" t="n">
-        <v>2317392</v>
+        <v>176616</v>
       </c>
       <c r="E6" t="n">
-        <v>944100</v>
+        <v>60300</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>68280</v>
+        <v>11220</v>
       </c>
       <c r="H6" t="n">
-        <v>7260</v>
+        <v>1380</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>107580</v>
+        <v>42600</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>17623.71</v>
+        <v>344.61</v>
       </c>
       <c r="C7" t="n">
-        <v>2805264</v>
+        <v>45360</v>
       </c>
       <c r="D7" t="n">
-        <v>2204136</v>
+        <v>35640</v>
       </c>
       <c r="E7" t="n">
-        <v>803700</v>
+        <v>4500</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>44460</v>
+        <v>1950</v>
       </c>
       <c r="H7" t="n">
-        <v>2430</v>
+        <v>420</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>102180</v>
+        <v>7830</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>16953.03</v>
+        <v>63.36</v>
       </c>
       <c r="C8" t="n">
-        <v>3041136</v>
+        <v>4032</v>
       </c>
       <c r="D8" t="n">
-        <v>2389464</v>
+        <v>3168</v>
       </c>
       <c r="E8" t="n">
-        <v>719100</v>
+        <v>900</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>41460</v>
+        <v>330</v>
       </c>
       <c r="H8" t="n">
-        <v>4380</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>109200</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9">
@@ -13761,37 +13755,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>21833.19</v>
+        <v>2.34</v>
       </c>
       <c r="C9" t="n">
-        <v>3519432</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2765268</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>778500</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>70890</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>10020</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>144720</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -13799,25 +13793,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>29727.81</v>
+        <v>0.09</v>
       </c>
       <c r="C10" t="n">
-        <v>4277448</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>3360852</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>838800</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>79320</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>11910</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>186630</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -13837,37 +13831,37 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>29466.63</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2706480</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2126520</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>306900</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>61140</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>129630</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -13875,37 +13869,37 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>25048.17</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1817928</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1428372</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>148500</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>35100</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>77010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,22 +13907,22 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>14693.49</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>939456</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>738144</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>25770</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13937,13 +13931,13 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>42060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,25 +13945,25 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>1829.43</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>116928</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>91872</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>11760</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,22 +13983,22 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>374.76</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>53424</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>41976</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4830</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>175.68</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11088</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8712</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>116.28</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14103,13 +14097,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>12.96</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14141,13 +14135,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>17.64</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14156,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -14171,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14179,13 +14173,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>10.62</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14194,7 +14188,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -14209,7 +14203,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -14217,13 +14211,13 @@
         <v>850</v>
       </c>
       <c r="B21" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14232,7 +14226,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -14247,7 +14241,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -14255,13 +14249,13 @@
         <v>900</v>
       </c>
       <c r="B22" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14270,7 +14264,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>3780</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -14285,7 +14279,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -14293,13 +14287,13 @@
         <v>950</v>
       </c>
       <c r="B23" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14308,7 +14302,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>9719.879999999999</v>
+        <v>12985.31</v>
       </c>
       <c r="C5" t="n">
-        <v>2217600</v>
+        <v>1133470.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1048608</v>
+        <v>535969.76</v>
       </c>
       <c r="E5" t="n">
-        <v>143246.61</v>
+        <v>42785.37</v>
       </c>
       <c r="F5" t="n">
-        <v>0.54</v>
+        <v>0.34</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1306.8</v>
+        <v>2797.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>27909</v>
+        <v>51748.2</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>15565.39</v>
+        <v>3066.12</v>
       </c>
       <c r="C6" t="n">
-        <v>2654467.2</v>
+        <v>202305.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1174917.74</v>
+        <v>89544.31</v>
       </c>
       <c r="E6" t="n">
-        <v>159552.9</v>
+        <v>10190.7</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>3414</v>
+        <v>561</v>
       </c>
       <c r="H6" t="n">
-        <v>4138.2</v>
+        <v>786.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>39804.6</v>
+        <v>15762</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>16742.52</v>
+        <v>327.38</v>
       </c>
       <c r="C7" t="n">
-        <v>2805264</v>
+        <v>45360</v>
       </c>
       <c r="D7" t="n">
-        <v>1406238.77</v>
+        <v>22738.32</v>
       </c>
       <c r="E7" t="n">
-        <v>170946.99</v>
+        <v>957.15</v>
       </c>
       <c r="F7" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>6669</v>
+        <v>292.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1773.9</v>
+        <v>306.6</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>61308</v>
+        <v>4698</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>16953.03</v>
+        <v>63.36</v>
       </c>
       <c r="C8" t="n">
-        <v>3041136</v>
+        <v>4032</v>
       </c>
       <c r="D8" t="n">
-        <v>1758645.5</v>
+        <v>2331.65</v>
       </c>
       <c r="E8" t="n">
-        <v>176395.23</v>
+        <v>220.77</v>
       </c>
       <c r="F8" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>26949</v>
+        <v>214.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3723</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>77532</v>
+        <v>852</v>
       </c>
     </row>
     <row r="9">
@@ -14693,37 +14687,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>21833.19</v>
+        <v>2.34</v>
       </c>
       <c r="C9" t="n">
-        <v>3519432</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2220510.2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>208404.45</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>60256.5</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
-        <v>10020</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>117223.2</v>
+        <v>194.4</v>
       </c>
     </row>
     <row r="10">
@@ -14731,25 +14725,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>29727.81</v>
+        <v>0.09</v>
       </c>
       <c r="C10" t="n">
-        <v>4277448</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2923941.24</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>243252</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>79320</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>11910</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>166100.7</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -14769,37 +14763,37 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>29466.63</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2706480</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1910678.22</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>125767.62</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>61140</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>129630</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -14807,37 +14801,37 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>25048.17</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1817928</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1324100.84</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>70983</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>35100</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>77010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,22 +14839,22 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>14693.49</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>939456</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>700867.73</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>26671.68</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>25770</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14869,13 +14863,13 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>42060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,25 +14877,25 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>1829.43</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>116928</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>89299.58</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>4098.96</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2550</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>11760</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,22 +14915,22 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>374.76</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>53424</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>41388.34</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>536.67</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1350</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4830</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>175.68</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11088</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8712</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>116.28</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15035,13 +15029,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>12.96</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>810</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15073,13 +15067,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>17.64</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15088,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -15103,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15111,13 +15105,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>10.62</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15126,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -15141,7 +15135,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -15149,13 +15143,13 @@
         <v>850</v>
       </c>
       <c r="B21" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15164,7 +15158,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -15179,7 +15173,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -15187,13 +15181,13 @@
         <v>900</v>
       </c>
       <c r="B22" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15202,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>3780</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -15217,7 +15211,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -15225,13 +15219,13 @@
         <v>950</v>
       </c>
       <c r="B23" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15240,7 +15234,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>21383732.7</v>
+        <v>28567687.5</v>
       </c>
       <c r="C5" t="n">
-        <v>121968000</v>
+        <v>62340894</v>
       </c>
       <c r="D5" t="n">
-        <v>106255448.64</v>
+        <v>54309816.19</v>
       </c>
       <c r="E5" t="n">
-        <v>26391755.43</v>
+        <v>7882776.57</v>
       </c>
       <c r="F5" t="n">
-        <v>22500.18</v>
+        <v>14166.78</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>361526.22</v>
+        <v>773845.38</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>52499.7</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>262902.78</v>
+        <v>487468.04</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>34243862.4</v>
+        <v>6745464</v>
       </c>
       <c r="C6" t="n">
-        <v>145995696</v>
+        <v>11126808</v>
       </c>
       <c r="D6" t="n">
-        <v>119054415</v>
+        <v>9073525.130000001</v>
       </c>
       <c r="E6" t="n">
-        <v>29396026.3</v>
+        <v>1877534.57</v>
       </c>
       <c r="F6" t="n">
-        <v>58333.8</v>
+        <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>63159</v>
+        <v>10378.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1144833.03</v>
+        <v>217612.89</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>379164.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>374959.33</v>
+        <v>148478.04</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>36833553.9</v>
+        <v>720234.9</v>
       </c>
       <c r="C7" t="n">
-        <v>154289520</v>
+        <v>2494800</v>
       </c>
       <c r="D7" t="n">
-        <v>142494174.36</v>
+        <v>2304073.97</v>
       </c>
       <c r="E7" t="n">
-        <v>31495273.44</v>
+        <v>176345.32</v>
       </c>
       <c r="F7" t="n">
-        <v>275002.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>123376.5</v>
+        <v>5411.25</v>
       </c>
       <c r="H7" t="n">
-        <v>490749.43</v>
+        <v>84820.89</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>163332.4</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>577521.36</v>
+        <v>44255.16</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>37296666</v>
+        <v>139392</v>
       </c>
       <c r="C8" t="n">
-        <v>167262480</v>
+        <v>221760</v>
       </c>
       <c r="D8" t="n">
-        <v>178203548.92</v>
+        <v>236265.89</v>
       </c>
       <c r="E8" t="n">
-        <v>32499057.18</v>
+        <v>40674.66</v>
       </c>
       <c r="F8" t="n">
-        <v>316669.2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>498556.5</v>
+        <v>3968.25</v>
       </c>
       <c r="H8" t="n">
-        <v>1029967.95</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>148749.15</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>730351.4399999999</v>
+        <v>8025.84</v>
       </c>
     </row>
     <row r="9">
@@ -15625,37 +15619,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>48033018</v>
+        <v>5148</v>
       </c>
       <c r="C9" t="n">
-        <v>193568760</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>225004298.97</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>38396435.87</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>541671</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1114745.25</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
-        <v>2772033</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>332498.1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1104242.54</v>
+        <v>1831.25</v>
       </c>
     </row>
     <row r="10">
@@ -15663,25 +15657,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>65401182</v>
+        <v>198</v>
       </c>
       <c r="C10" t="n">
-        <v>235259640</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>296282965.85</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>44816748.48</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>83334</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1467420</v>
+        <v>555</v>
       </c>
       <c r="H10" t="n">
-        <v>3294901.5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15693,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1564668.59</v>
+        <v>754.54</v>
       </c>
     </row>
     <row r="11">
@@ -15701,4697 +15695,37 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>64826586</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>148856400</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>193609024.03</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>23171426.31</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1131090</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>248985</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>116666</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1221114.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>55105974</v>
-      </c>
-      <c r="C12" t="n">
-        <v>99986040</v>
-      </c>
-      <c r="D12" t="n">
-        <v>134171138.52</v>
-      </c>
-      <c r="E12" t="n">
-        <v>13077907.92</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>649350</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8299.5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>116666</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>725434.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>32325678</v>
-      </c>
-      <c r="C13" t="n">
-        <v>51670080</v>
-      </c>
-      <c r="D13" t="n">
-        <v>71018926.88</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4913990.32</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>476745</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>58333</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>396205.2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>4024746</v>
-      </c>
-      <c r="C14" t="n">
-        <v>6431040</v>
-      </c>
-      <c r="D14" t="n">
-        <v>9048726.85</v>
-      </c>
-      <c r="E14" t="n">
-        <v>755192.39</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>47175</v>
-      </c>
-      <c r="H14" t="n">
-        <v>8299.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>110779.2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>824472</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2938320</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4193880.09</v>
-      </c>
-      <c r="E15" t="n">
-        <v>98876.08</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>24975</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>45498.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>386496</v>
-      </c>
-      <c r="C16" t="n">
-        <v>609840</v>
-      </c>
-      <c r="D16" t="n">
-        <v>882786.96</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6105</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>28260</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>255816</v>
-      </c>
-      <c r="C17" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D17" t="n">
-        <v>120380.04</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4995</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>7912.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>28512</v>
-      </c>
-      <c r="C18" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D18" t="n">
-        <v>160506.72</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2220</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7630.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>38808</v>
-      </c>
-      <c r="C19" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D19" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>23364</v>
-      </c>
-      <c r="C20" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D20" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1110</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>12276</v>
-      </c>
-      <c r="C21" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D21" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>5934.6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>3762</v>
-      </c>
-      <c r="C22" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D22" t="n">
-        <v>280886.76</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>69930</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3108.6</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>198</v>
-      </c>
-      <c r="C23" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D23" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>555</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D24" t="n">
-        <v>280886.76</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2509.11</v>
-      </c>
-      <c r="C4" t="n">
-        <v>997920</v>
-      </c>
-      <c r="D4" t="n">
-        <v>784080</v>
-      </c>
-      <c r="E4" t="n">
-        <v>442800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>14100</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1860</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>25710</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5367.33</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1546776</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1215324</v>
-      </c>
-      <c r="E5" t="n">
-        <v>472500</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>20370</v>
-      </c>
-      <c r="H5" t="n">
-        <v>9870</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>49260</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4313.52</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1156680</v>
-      </c>
-      <c r="D6" t="n">
-        <v>908820</v>
-      </c>
-      <c r="E6" t="n">
-        <v>350100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>13</v>
-      </c>
-      <c r="G6" t="n">
-        <v>15420</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3960</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>33090</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4028.4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>820512</v>
-      </c>
-      <c r="D7" t="n">
-        <v>644688</v>
-      </c>
-      <c r="E7" t="n">
-        <v>174600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>12930</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1350</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>26640</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>3814.65</v>
-      </c>
-      <c r="C8" t="n">
-        <v>604296</v>
-      </c>
-      <c r="D8" t="n">
-        <v>474804</v>
-      </c>
-      <c r="E8" t="n">
-        <v>134100</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="n">
-        <v>11250</v>
-      </c>
-      <c r="H8" t="n">
-        <v>990</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>22980</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3184.47</v>
-      </c>
-      <c r="C9" t="n">
-        <v>351792</v>
-      </c>
-      <c r="D9" t="n">
-        <v>276408</v>
-      </c>
-      <c r="E9" t="n">
-        <v>51300</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6660</v>
-      </c>
-      <c r="H9" t="n">
-        <v>780</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>16800</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3521.16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>256536</v>
-      </c>
-      <c r="D10" t="n">
-        <v>201564</v>
-      </c>
-      <c r="E10" t="n">
-        <v>49500</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3630</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>10350</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3958.65</v>
-      </c>
-      <c r="C11" t="n">
-        <v>212184</v>
-      </c>
-      <c r="D11" t="n">
-        <v>166716</v>
-      </c>
-      <c r="E11" t="n">
-        <v>39600</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2610</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>8010</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>3925.35</v>
-      </c>
-      <c r="C12" t="n">
-        <v>190512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>149688</v>
-      </c>
-      <c r="E12" t="n">
-        <v>18900</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4980</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>11100</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2619.72</v>
-      </c>
-      <c r="C13" t="n">
-        <v>69552</v>
-      </c>
-      <c r="D13" t="n">
-        <v>54648</v>
-      </c>
-      <c r="E13" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1530</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3750</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1639.26</v>
-      </c>
-      <c r="C14" t="n">
-        <v>34272</v>
-      </c>
-      <c r="D14" t="n">
-        <v>26928</v>
-      </c>
-      <c r="E14" t="n">
-        <v>900</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>360</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>931.59</v>
-      </c>
-      <c r="C15" t="n">
-        <v>6552</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5148</v>
-      </c>
-      <c r="E15" t="n">
-        <v>900</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>180</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>585.72</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3168</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>434.07</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>293.94</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>422.91</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D19" t="n">
-        <v>792</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>241.47</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D20" t="n">
-        <v>792</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>108.45</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D21" t="n">
-        <v>792</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>42.39</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2415.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>850726.8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>402272.24</v>
-      </c>
-      <c r="E5" t="n">
-        <v>52116.75</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3553.2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>10344.6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3450.82</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1041012</v>
-      </c>
-      <c r="D6" t="n">
-        <v>460771.74</v>
-      </c>
-      <c r="E6" t="n">
-        <v>59166.9</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>771</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2257.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>12243.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3826.98</v>
-      </c>
-      <c r="C7" t="n">
-        <v>820512</v>
-      </c>
-      <c r="D7" t="n">
-        <v>411310.94</v>
-      </c>
-      <c r="E7" t="n">
-        <v>37137.42</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1939.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>985.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>15984</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>3814.65</v>
-      </c>
-      <c r="C8" t="n">
-        <v>604296</v>
-      </c>
-      <c r="D8" t="n">
-        <v>349455.74</v>
-      </c>
-      <c r="E8" t="n">
-        <v>32894.73</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G8" t="n">
-        <v>7312.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>841.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>16315.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3184.47</v>
-      </c>
-      <c r="C9" t="n">
-        <v>351792</v>
-      </c>
-      <c r="D9" t="n">
-        <v>221955.62</v>
-      </c>
-      <c r="E9" t="n">
-        <v>13733.01</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5661</v>
-      </c>
-      <c r="H9" t="n">
-        <v>780</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>13608</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3521.16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>256536</v>
-      </c>
-      <c r="D10" t="n">
-        <v>175360.68</v>
-      </c>
-      <c r="E10" t="n">
-        <v>14355</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3630</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>9211.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3958.65</v>
-      </c>
-      <c r="C11" t="n">
-        <v>212184</v>
-      </c>
-      <c r="D11" t="n">
-        <v>149794.33</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16228.08</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2610</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>8010</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>3925.35</v>
-      </c>
-      <c r="C12" t="n">
-        <v>190512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>138760.78</v>
-      </c>
-      <c r="E12" t="n">
-        <v>9034.200000000001</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4980</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>11100</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2619.72</v>
-      </c>
-      <c r="C13" t="n">
-        <v>69552</v>
-      </c>
-      <c r="D13" t="n">
-        <v>51888.28</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2381.4</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1530</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>3750</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1639.26</v>
-      </c>
-      <c r="C14" t="n">
-        <v>34272</v>
-      </c>
-      <c r="D14" t="n">
-        <v>26174.02</v>
-      </c>
-      <c r="E14" t="n">
-        <v>512.37</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>360</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>931.59</v>
-      </c>
-      <c r="C15" t="n">
-        <v>6552</v>
-      </c>
-      <c r="D15" t="n">
-        <v>5075.93</v>
-      </c>
-      <c r="E15" t="n">
-        <v>536.67</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>180</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>585.72</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3168</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>434.07</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>293.94</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>422.91</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D19" t="n">
-        <v>792</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>241.47</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D20" t="n">
-        <v>792</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>108.45</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D21" t="n">
-        <v>792</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>42.39</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5313656.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>46789974</v>
-      </c>
-      <c r="D5" t="n">
-        <v>40762246.48</v>
-      </c>
-      <c r="E5" t="n">
-        <v>9601990.02</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5833.38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>982992.78</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>69999.60000000001</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>97446.13</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7591795.2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>57255660</v>
-      </c>
-      <c r="D6" t="n">
-        <v>46690000.41</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10900909.66</v>
-      </c>
-      <c r="F6" t="n">
-        <v>54167.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>14263.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>624454.38</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>58333</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>115331.89</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8419356</v>
-      </c>
-      <c r="C7" t="n">
-        <v>45128160</v>
-      </c>
-      <c r="D7" t="n">
-        <v>41678137.96</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6842198.26</v>
-      </c>
-      <c r="F7" t="n">
-        <v>100000.8</v>
-      </c>
-      <c r="G7" t="n">
-        <v>35880.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>272638.57</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>150569.28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>8392230</v>
-      </c>
-      <c r="C8" t="n">
-        <v>33236280</v>
-      </c>
-      <c r="D8" t="n">
-        <v>35410350.54</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6060525.06</v>
-      </c>
-      <c r="F8" t="n">
-        <v>237501.9</v>
-      </c>
-      <c r="G8" t="n">
-        <v>135281.25</v>
-      </c>
-      <c r="H8" t="n">
-        <v>232800.97</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>49583.05</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>153694.84</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>7005834</v>
-      </c>
-      <c r="C9" t="n">
-        <v>19348560</v>
-      </c>
-      <c r="D9" t="n">
-        <v>22490763.38</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2530169.76</v>
-      </c>
-      <c r="F9" t="n">
-        <v>125001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>104728.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>215787</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>128187.36</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>7746552</v>
-      </c>
-      <c r="C10" t="n">
-        <v>14109480</v>
-      </c>
-      <c r="D10" t="n">
-        <v>17769297.7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2644765.2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>67155</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>86772.33</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>8709030</v>
-      </c>
-      <c r="C11" t="n">
-        <v>11670120</v>
-      </c>
-      <c r="D11" t="n">
-        <v>15178659.05</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2989861.46</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G11" t="n">
-        <v>48285</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>75454.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>8635770</v>
-      </c>
-      <c r="C12" t="n">
-        <v>10478160</v>
-      </c>
-      <c r="D12" t="n">
-        <v>14060629.43</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1664461.01</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>92130</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>104562</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>5763384</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3825360</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5257839.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>438749.14</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>28305</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>35325</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>3606372</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1884960</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2652213.04</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6660</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6499.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2049498</v>
-      </c>
-      <c r="C15" t="n">
-        <v>360360</v>
-      </c>
-      <c r="D15" t="n">
-        <v>514343.78</v>
-      </c>
-      <c r="E15" t="n">
-        <v>98876.08</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1413</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>1288584</v>
-      </c>
-      <c r="C16" t="n">
-        <v>221760</v>
-      </c>
-      <c r="D16" t="n">
-        <v>321013.44</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>954954</v>
-      </c>
-      <c r="C17" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D17" t="n">
-        <v>200633.4</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>646668</v>
-      </c>
-      <c r="C18" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D18" t="n">
-        <v>120380.04</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>930402</v>
-      </c>
-      <c r="C19" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D19" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>531234</v>
-      </c>
-      <c r="C20" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D20" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>238590</v>
-      </c>
-      <c r="C21" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D21" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>93258</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>46396.89</v>
-      </c>
-      <c r="C4" t="n">
-        <v>6009192</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4721508</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1489500</v>
-      </c>
-      <c r="F4" t="n">
-        <v>46</v>
-      </c>
-      <c r="G4" t="n">
-        <v>146730</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23130</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>438840</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>28856.25</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2060856</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1619244</v>
-      </c>
-      <c r="E5" t="n">
-        <v>387900</v>
-      </c>
-      <c r="F5" t="n">
-        <v>17</v>
-      </c>
-      <c r="G5" t="n">
-        <v>71820</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7770</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>246420</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3832.65</v>
-      </c>
-      <c r="C6" t="n">
-        <v>224784</v>
-      </c>
-      <c r="D6" t="n">
-        <v>176616</v>
-      </c>
-      <c r="E6" t="n">
-        <v>60300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11220</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1380</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>42600</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>344.61</v>
-      </c>
-      <c r="C7" t="n">
-        <v>45360</v>
-      </c>
-      <c r="D7" t="n">
-        <v>35640</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1950</v>
-      </c>
-      <c r="H7" t="n">
-        <v>420</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>7830</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>63.36</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3168</v>
-      </c>
-      <c r="E8" t="n">
-        <v>900</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>330</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>12985.31</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1133470.8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>535969.76</v>
-      </c>
-      <c r="E5" t="n">
-        <v>42785.37</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2797.2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>51748.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3066.12</v>
-      </c>
-      <c r="C6" t="n">
-        <v>202305.6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>89544.31</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10190.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>561</v>
-      </c>
-      <c r="H6" t="n">
-        <v>786.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>15762</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>327.38</v>
-      </c>
-      <c r="C7" t="n">
-        <v>45360</v>
-      </c>
-      <c r="D7" t="n">
-        <v>22738.32</v>
-      </c>
-      <c r="E7" t="n">
-        <v>957.15</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>292.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>306.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4698</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>63.36</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2331.65</v>
-      </c>
-      <c r="E8" t="n">
-        <v>220.77</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>214.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>194.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>80.09999999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>180</v>
+        <v>1695.6</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>28567687.5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>62340894</v>
-      </c>
-      <c r="D5" t="n">
-        <v>54309816.19</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7882776.57</v>
-      </c>
-      <c r="F5" t="n">
-        <v>14166.78</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>773845.38</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>487468.04</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>6745464</v>
-      </c>
-      <c r="C6" t="n">
-        <v>11126808</v>
-      </c>
-      <c r="D6" t="n">
-        <v>9073525.130000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1877534.57</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4166.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>10378.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>217612.89</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>148478.04</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>720234.9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2494800</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2304073.97</v>
-      </c>
-      <c r="E7" t="n">
-        <v>176345.32</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5411.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>84820.89</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>44255.16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>139392</v>
-      </c>
-      <c r="C8" t="n">
-        <v>221760</v>
-      </c>
-      <c r="D8" t="n">
-        <v>236265.89</v>
-      </c>
-      <c r="E8" t="n">
-        <v>40674.66</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3968.25</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8025.84</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>5148</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1831.25</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>198</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>555</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>754.54</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1695.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_500yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_500yrs_Future_Breaches.xlsx
@@ -538,7 +538,7 @@
         <v>75330</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>28</v>
@@ -576,7 +576,7 @@
         <v>54120</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>31</v>
@@ -614,7 +614,7 @@
         <v>39030</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
         <v>22</v>
@@ -652,7 +652,7 @@
         <v>28410</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>13</v>
@@ -690,7 +690,7 @@
         <v>40230</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>13</v>
@@ -728,7 +728,7 @@
         <v>39210</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>10</v>
@@ -766,7 +766,7 @@
         <v>30570</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
@@ -804,7 +804,7 @@
         <v>23760</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>6</v>
@@ -842,7 +842,7 @@
         <v>5910</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>7</v>
@@ -918,7 +918,7 @@
         <v>5520</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
@@ -1032,7 +1032,7 @@
         <v>840</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1774,7 +1774,7 @@
         <v>3120</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -1850,7 +1850,7 @@
         <v>5280</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>2</v>
@@ -1964,7 +1964,7 @@
         <v>840</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>3120</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -2782,7 +2782,7 @@
         <v>5280</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>2</v>
@@ -2896,7 +2896,7 @@
         <v>840</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>863148</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J12" t="n">
         <v>116666</v>
@@ -3714,7 +3714,7 @@
         <v>1460712</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>766660</v>
       </c>
       <c r="J14" t="n">
         <v>116666</v>
@@ -3828,7 +3828,7 @@
         <v>232386</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>6000</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
@@ -9896,7 +9896,7 @@
         <v>3630</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -9934,7 +9934,7 @@
         <v>7260</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
         <v>13</v>
@@ -9972,7 +9972,7 @@
         <v>2430</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
@@ -10010,7 +10010,7 @@
         <v>4380</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -10048,7 +10048,7 @@
         <v>10020</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>6</v>
@@ -10086,7 +10086,7 @@
         <v>11910</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -10124,7 +10124,7 @@
         <v>900</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -10238,7 +10238,7 @@
         <v>30</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>19483.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J5" t="n">
         <v>9.300000000000001</v>
@@ -10866,7 +10866,7 @@
         <v>22247.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="J6" t="n">
         <v>11</v>
@@ -10904,7 +10904,7 @@
         <v>20739.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="J7" t="n">
         <v>9.1</v>
@@ -10942,7 +10942,7 @@
         <v>34195.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="J8" t="n">
         <v>11.05</v>
@@ -10980,7 +10980,7 @@
         <v>39210</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>9.5</v>
@@ -11018,7 +11018,7 @@
         <v>30570</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="J10" t="n">
         <v>9</v>
@@ -11056,7 +11056,7 @@
         <v>23760</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>6</v>
@@ -11094,7 +11094,7 @@
         <v>5910</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>7</v>
@@ -11170,7 +11170,7 @@
         <v>5520</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
@@ -11284,7 +11284,7 @@
         <v>840</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>1306.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>0.9</v>
@@ -11798,7 +11798,7 @@
         <v>4138.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J6" t="n">
         <v>6.5</v>
@@ -11836,7 +11836,7 @@
         <v>1773.9</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>2.8</v>
@@ -11874,7 +11874,7 @@
         <v>3723</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="J8" t="n">
         <v>2.55</v>
@@ -11912,7 +11912,7 @@
         <v>10020</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>5.7</v>
@@ -11950,7 +11950,7 @@
         <v>11910</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -11988,7 +11988,7 @@
         <v>900</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -12102,7 +12102,7 @@
         <v>30</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>361526.22</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>52499.7</v>
@@ -12730,7 +12730,7 @@
         <v>1144833.03</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>804993</v>
       </c>
       <c r="J6" t="n">
         <v>379164.5</v>
@@ -12768,7 +12768,7 @@
         <v>490749.43</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>163332.4</v>
@@ -12806,7 +12806,7 @@
         <v>1029967.95</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>827992.8</v>
       </c>
       <c r="J8" t="n">
         <v>148749.15</v>
@@ -12844,7 +12844,7 @@
         <v>2772033</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>332498.1</v>
@@ -12882,7 +12882,7 @@
         <v>3294901.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>735993.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -12920,7 +12920,7 @@
         <v>248985</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>766660</v>
       </c>
       <c r="J11" t="n">
         <v>116666</v>
@@ -13034,7 +13034,7 @@
         <v>8299.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -13586,7 +13586,7 @@
         <v>23130</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>7</v>
@@ -16420,7 +16420,7 @@
         <v>5390027.28</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>172498.5</v>
       </c>
       <c r="J5" t="n">
         <v>542496.9</v>
@@ -16458,7 +16458,7 @@
         <v>6154660.21</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>939158.5</v>
       </c>
       <c r="J6" t="n">
         <v>641663</v>
@@ -16496,7 +16496,7 @@
         <v>5737527.34</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>632494.5</v>
       </c>
       <c r="J7" t="n">
         <v>530830.3</v>
@@ -16534,7 +16534,7 @@
         <v>9460185.07</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>827992.8</v>
       </c>
       <c r="J8" t="n">
         <v>644579.65</v>
@@ -16572,7 +16572,7 @@
         <v>10847446.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>554163.5</v>
@@ -16610,7 +16610,7 @@
         <v>8457190.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>735993.6</v>
       </c>
       <c r="J10" t="n">
         <v>524997</v>
@@ -16648,7 +16648,7 @@
         <v>6573204</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1149990</v>
       </c>
       <c r="J11" t="n">
         <v>349998</v>
@@ -16686,7 +16686,7 @@
         <v>1635001.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J12" t="n">
         <v>408331</v>
@@ -16762,7 +16762,7 @@
         <v>1527108</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1149990</v>
       </c>
       <c r="J14" t="n">
         <v>174999</v>
@@ -16876,7 +16876,7 @@
         <v>232386</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -17352,7 +17352,7 @@
         <v>1680</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -17428,7 +17428,7 @@
         <v>3390</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -17580,7 +17580,7 @@
         <v>17730</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -18284,7 +18284,7 @@
         <v>604.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>0.9</v>
@@ -18360,7 +18360,7 @@
         <v>2474.7</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J7" t="n">
         <v>0.7</v>
@@ -18512,7 +18512,7 @@
         <v>17730</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -19216,7 +19216,7 @@
         <v>167317.92</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>52499.7</v>
@@ -19292,7 +19292,7 @@
         <v>684625.75</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>210831.5</v>
       </c>
       <c r="J7" t="n">
         <v>40833.1</v>
@@ -19444,7 +19444,7 @@
         <v>4905004.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>174999</v>
@@ -20148,7 +20148,7 @@
         <v>16500</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>13</v>
@@ -20186,7 +20186,7 @@
         <v>15000</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
@@ -21080,7 +21080,7 @@
         <v>5940</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>3.9</v>
@@ -21118,7 +21118,7 @@
         <v>8550</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -22012,7 +22012,7 @@
         <v>1643301</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>227498.7</v>
@@ -22050,7 +22050,7 @@
         <v>2365357.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>116666</v>

--- a/risk/Risk_Analysis_T3_500yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_500yrs_Future_Breaches.xlsx
@@ -544,7 +544,7 @@
         <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1102</v>
       </c>
       <c r="L4" t="n">
         <v>1361520</v>
@@ -582,7 +582,7 @@
         <v>31</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="L5" t="n">
         <v>1074450</v>
@@ -620,7 +620,7 @@
         <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="L6" t="n">
         <v>604050</v>
@@ -658,7 +658,7 @@
         <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="L7" t="n">
         <v>492780</v>
@@ -696,7 +696,7 @@
         <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="L8" t="n">
         <v>411270</v>
@@ -734,7 +734,7 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="L9" t="n">
         <v>457860</v>
@@ -772,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="L10" t="n">
         <v>446460</v>
@@ -810,7 +810,7 @@
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="L11" t="n">
         <v>422280</v>
@@ -848,7 +848,7 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="L12" t="n">
         <v>386850</v>
@@ -886,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="L13" t="n">
         <v>292260</v>
@@ -924,7 +924,7 @@
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="L14" t="n">
         <v>167730</v>
@@ -962,7 +962,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="L15" t="n">
         <v>134370</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L16" t="n">
         <v>70650</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L17" t="n">
         <v>33180</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
         <v>14130</v>
@@ -1114,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
         <v>5400</v>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>4260</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>14850</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>13710</v>
@@ -1552,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>15630</v>
@@ -1590,7 +1590,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
         <v>14550</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
         <v>16020</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L9" t="n">
         <v>20790</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
         <v>28140</v>
@@ -1742,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
         <v>38910</v>
@@ -1780,7 +1780,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
         <v>46470</v>
@@ -1818,7 +1818,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L13" t="n">
         <v>43440</v>
@@ -1856,7 +1856,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L14" t="n">
         <v>70020</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L15" t="n">
         <v>92880</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L16" t="n">
         <v>54990</v>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L17" t="n">
         <v>26490</v>
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L18" t="n">
         <v>11340</v>
@@ -2046,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>4380</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>3360</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="L5" t="n">
         <v>2879.1</v>
@@ -2484,7 +2484,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="L6" t="n">
         <v>5783.1</v>
@@ -2522,7 +2522,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6.56</v>
       </c>
       <c r="L7" t="n">
         <v>8730</v>
@@ -2560,7 +2560,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="L8" t="n">
         <v>11374.2</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L9" t="n">
         <v>16839.9</v>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
         <v>25044.6</v>
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
         <v>38910</v>
@@ -2712,7 +2712,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
         <v>46470</v>
@@ -2750,7 +2750,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L13" t="n">
         <v>43440</v>
@@ -2788,7 +2788,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L14" t="n">
         <v>70020</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L15" t="n">
         <v>92880</v>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L16" t="n">
         <v>54990</v>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L17" t="n">
         <v>26490</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L18" t="n">
         <v>11340</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>4380</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>3360</v>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>80642.52</v>
       </c>
       <c r="L5" t="n">
         <v>27121.12</v>
@@ -3416,7 +3416,7 @@
         <v>29166.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>124803.9</v>
       </c>
       <c r="L6" t="n">
         <v>54476.8</v>
@@ -3454,7 +3454,7 @@
         <v>40833.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>139951.04</v>
       </c>
       <c r="L7" t="n">
         <v>82236.60000000001</v>
@@ -3492,7 +3492,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>230407.2</v>
       </c>
       <c r="L8" t="n">
         <v>107144.96</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>362678</v>
       </c>
       <c r="L9" t="n">
         <v>158631.86</v>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>362678</v>
       </c>
       <c r="L10" t="n">
         <v>235920.13</v>
@@ -3606,7 +3606,7 @@
         <v>58333</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>426680</v>
       </c>
       <c r="L11" t="n">
         <v>366532.2</v>
@@ -3644,7 +3644,7 @@
         <v>116666</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>533350</v>
       </c>
       <c r="L12" t="n">
         <v>437747.4</v>
@@ -3682,7 +3682,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>512016</v>
       </c>
       <c r="L13" t="n">
         <v>409204.8</v>
@@ -3720,7 +3720,7 @@
         <v>116666</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>682688</v>
       </c>
       <c r="L14" t="n">
         <v>659588.4</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>896028</v>
       </c>
       <c r="L15" t="n">
         <v>874929.6</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>597352</v>
       </c>
       <c r="L16" t="n">
         <v>518005.8</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>256008</v>
       </c>
       <c r="L17" t="n">
         <v>249535.8</v>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>192006</v>
       </c>
       <c r="L18" t="n">
         <v>106822.8</v>
@@ -3910,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L19" t="n">
         <v>41259.6</v>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L21" t="n">
         <v>31651.2</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="L4" t="n">
         <v>185190</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="L5" t="n">
         <v>105960</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
         <v>28830</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>11880</v>
@@ -4424,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>1380</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>26.46</v>
       </c>
       <c r="L5" t="n">
         <v>22251.6</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="L6" t="n">
         <v>10667.1</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="L7" t="n">
         <v>7128</v>
@@ -5356,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="L8" t="n">
         <v>979.8</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>564497.64</v>
       </c>
       <c r="L5" t="n">
         <v>209610.07</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>208006.5</v>
       </c>
       <c r="L6" t="n">
         <v>100484.08</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>69975.52</v>
       </c>
       <c r="L7" t="n">
         <v>67145.75999999999</v>
@@ -6288,7 +6288,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>19200.6</v>
       </c>
       <c r="L8" t="n">
         <v>9229.719999999999</v>
@@ -7068,7 +7068,7 @@
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="L4" t="n">
         <v>191190</v>
@@ -7106,7 +7106,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="L5" t="n">
         <v>101730</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
         <v>31080</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>7380</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>3990</v>
@@ -8038,7 +8038,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>52.08</v>
       </c>
       <c r="L5" t="n">
         <v>21363.3</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>21.45</v>
       </c>
       <c r="L6" t="n">
         <v>11499.6</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>4428</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>2832.9</v>
@@ -8970,7 +8970,7 @@
         <v>139999.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1111074.72</v>
       </c>
       <c r="L5" t="n">
         <v>201242.29</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>457614.3</v>
       </c>
       <c r="L6" t="n">
         <v>108326.23</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>87469.39999999999</v>
       </c>
       <c r="L7" t="n">
         <v>41711.76</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>76802.39999999999</v>
       </c>
       <c r="L8" t="n">
         <v>26685.92</v>
@@ -9864,7 +9864,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="L4" t="n">
         <v>133800</v>
@@ -9902,7 +9902,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="L5" t="n">
         <v>132900</v>
@@ -9940,7 +9940,7 @@
         <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="L6" t="n">
         <v>107580</v>
@@ -9978,7 +9978,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="L7" t="n">
         <v>102180</v>
@@ -10016,7 +10016,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="L8" t="n">
         <v>109200</v>
@@ -10054,7 +10054,7 @@
         <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="L9" t="n">
         <v>144720</v>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="L10" t="n">
         <v>186630</v>
@@ -10130,7 +10130,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="L11" t="n">
         <v>129630</v>
@@ -10168,7 +10168,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L12" t="n">
         <v>77010</v>
@@ -10206,7 +10206,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L13" t="n">
         <v>42060</v>
@@ -10244,7 +10244,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
         <v>11760</v>
@@ -10282,7 +10282,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>4830</v>
@@ -10510,7 +10510,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>630</v>
@@ -10834,7 +10834,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>342.72</v>
       </c>
       <c r="L5" t="n">
         <v>225634.5</v>
@@ -10872,7 +10872,7 @@
         <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>319.15</v>
       </c>
       <c r="L6" t="n">
         <v>223498.5</v>
@@ -10910,7 +10910,7 @@
         <v>9.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>321.44</v>
       </c>
       <c r="L7" t="n">
         <v>295668</v>
@@ -10948,7 +10948,7 @@
         <v>11.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>314.1</v>
       </c>
       <c r="L8" t="n">
         <v>292001.7</v>
@@ -10986,7 +10986,7 @@
         <v>9.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="L9" t="n">
         <v>370866.6</v>
@@ -11024,7 +11024,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="L10" t="n">
         <v>397349.4</v>
@@ -11062,7 +11062,7 @@
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
       <c r="L11" t="n">
         <v>422280</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="L12" t="n">
         <v>386850</v>
@@ -11138,7 +11138,7 @@
         <v>9</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>286</v>
       </c>
       <c r="L13" t="n">
         <v>292260</v>
@@ -11176,7 +11176,7 @@
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="L14" t="n">
         <v>167730</v>
@@ -11214,7 +11214,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="L15" t="n">
         <v>134370</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L16" t="n">
         <v>70650</v>
@@ -11290,7 +11290,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L17" t="n">
         <v>33180</v>
@@ -11328,7 +11328,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
         <v>14130</v>
@@ -11366,7 +11366,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" t="n">
         <v>5400</v>
@@ -11442,7 +11442,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>4260</v>
@@ -11766,7 +11766,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>70.98</v>
       </c>
       <c r="L5" t="n">
         <v>27909</v>
@@ -11804,7 +11804,7 @@
         <v>6.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>84.5</v>
       </c>
       <c r="L6" t="n">
         <v>39804.6</v>
@@ -11842,7 +11842,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>102.5</v>
       </c>
       <c r="L7" t="n">
         <v>61308</v>
@@ -11880,7 +11880,7 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="L8" t="n">
         <v>77532</v>
@@ -11918,7 +11918,7 @@
         <v>5.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="L9" t="n">
         <v>117223.2</v>
@@ -11956,7 +11956,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="L10" t="n">
         <v>166100.7</v>
@@ -11994,7 +11994,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="L11" t="n">
         <v>129630</v>
@@ -12032,7 +12032,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L12" t="n">
         <v>77010</v>
@@ -12070,7 +12070,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L13" t="n">
         <v>42060</v>
@@ -12108,7 +12108,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L14" t="n">
         <v>11760</v>
@@ -12146,7 +12146,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>4830</v>
@@ -12374,7 +12374,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>630</v>
@@ -12698,7 +12698,7 @@
         <v>52499.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1514287.32</v>
       </c>
       <c r="L5" t="n">
         <v>262902.78</v>
@@ -12736,7 +12736,7 @@
         <v>379164.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1802723</v>
       </c>
       <c r="L6" t="n">
         <v>374959.33</v>
@@ -12774,7 +12774,7 @@
         <v>163332.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2186735</v>
       </c>
       <c r="L7" t="n">
         <v>577521.36</v>
@@ -12812,7 +12812,7 @@
         <v>148749.15</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2400075</v>
       </c>
       <c r="L8" t="n">
         <v>730351.4399999999</v>
@@ -12850,7 +12850,7 @@
         <v>332498.1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2474744</v>
       </c>
       <c r="L9" t="n">
         <v>1104242.54</v>
@@ -12888,7 +12888,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4416138</v>
       </c>
       <c r="L10" t="n">
         <v>1564668.59</v>
@@ -12926,7 +12926,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2816088</v>
       </c>
       <c r="L11" t="n">
         <v>1221114.6</v>
@@ -12964,7 +12964,7 @@
         <v>116666</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2048064</v>
       </c>
       <c r="L12" t="n">
         <v>725434.2</v>
@@ -13002,7 +13002,7 @@
         <v>58333</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1045366</v>
       </c>
       <c r="L13" t="n">
         <v>396205.2</v>
@@ -13040,7 +13040,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>128004</v>
       </c>
       <c r="L14" t="n">
         <v>110779.2</v>
@@ -13078,7 +13078,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L15" t="n">
         <v>45498.6</v>
@@ -13306,7 +13306,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L21" t="n">
         <v>5934.6</v>
@@ -13592,7 +13592,7 @@
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="L4" t="n">
         <v>438840</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="L5" t="n">
         <v>246420</v>
@@ -13668,7 +13668,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>42600</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>29.82</v>
       </c>
       <c r="L5" t="n">
         <v>51748.2</v>
@@ -14600,7 +14600,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>15762</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>636179.88</v>
       </c>
       <c r="L5" t="n">
         <v>487468.04</v>
@@ -15532,7 +15532,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>83202.60000000001</v>
       </c>
       <c r="L6" t="n">
         <v>148478.04</v>
@@ -16426,7 +16426,7 @@
         <v>542496.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>7311588.48</v>
       </c>
       <c r="L5" t="n">
         <v>2125476.99</v>
@@ -16464,7 +16464,7 @@
         <v>641663</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6808746.1</v>
       </c>
       <c r="L6" t="n">
         <v>2105355.87</v>
@@ -16502,7 +16502,7 @@
         <v>530830.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>6857600.96</v>
       </c>
       <c r="L7" t="n">
         <v>2785192.56</v>
@@ -16540,7 +16540,7 @@
         <v>644579.65</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6701009.4</v>
       </c>
       <c r="L8" t="n">
         <v>2750656.01</v>
@@ -16578,7 +16578,7 @@
         <v>554163.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7189558</v>
       </c>
       <c r="L9" t="n">
         <v>3493563.37</v>
@@ -16616,7 +16616,7 @@
         <v>524997</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>8725606</v>
       </c>
       <c r="L10" t="n">
         <v>3743031.35</v>
@@ -16654,7 +16654,7 @@
         <v>349998</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>7552236</v>
       </c>
       <c r="L11" t="n">
         <v>3977877.6</v>
@@ -16692,7 +16692,7 @@
         <v>408331</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>7317562</v>
       </c>
       <c r="L12" t="n">
         <v>3644127</v>
@@ -16730,7 +16730,7 @@
         <v>524997</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>6101524</v>
       </c>
       <c r="L13" t="n">
         <v>2753089.2</v>
@@ -16768,7 +16768,7 @@
         <v>174999</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2880090</v>
       </c>
       <c r="L14" t="n">
         <v>1580016.6</v>
@@ -16806,7 +16806,7 @@
         <v>174999</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1834724</v>
       </c>
       <c r="L15" t="n">
         <v>1265765.4</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>832026</v>
       </c>
       <c r="L16" t="n">
         <v>665523</v>
@@ -16882,7 +16882,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>384012</v>
       </c>
       <c r="L17" t="n">
         <v>312555.6</v>
@@ -16920,7 +16920,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L18" t="n">
         <v>133104.6</v>
@@ -16958,7 +16958,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L19" t="n">
         <v>50868</v>
@@ -17034,7 +17034,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L21" t="n">
         <v>40129.2</v>
@@ -17320,7 +17320,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L4" t="n">
         <v>56400</v>
@@ -17358,7 +17358,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="L5" t="n">
         <v>71100</v>
@@ -17396,7 +17396,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="L6" t="n">
         <v>97320</v>
@@ -17434,7 +17434,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="L7" t="n">
         <v>140730</v>
@@ -17472,7 +17472,7 @@
         <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="L8" t="n">
         <v>140580</v>
@@ -17510,7 +17510,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="L9" t="n">
         <v>166530</v>
@@ -17548,7 +17548,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="L10" t="n">
         <v>179580</v>
@@ -17586,7 +17586,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="L11" t="n">
         <v>239880</v>
@@ -17624,7 +17624,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="L12" t="n">
         <v>250110</v>
@@ -17662,7 +17662,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="L13" t="n">
         <v>201870</v>
@@ -17700,7 +17700,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="L14" t="n">
         <v>84420</v>
@@ -17738,7 +17738,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L15" t="n">
         <v>36510</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L16" t="n">
         <v>12660</v>
@@ -17814,7 +17814,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
         <v>5850</v>
@@ -17852,7 +17852,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>1980</v>
@@ -17890,7 +17890,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>720</v>
@@ -18290,7 +18290,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>35.28</v>
       </c>
       <c r="L5" t="n">
         <v>14931</v>
@@ -18328,7 +18328,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>61.1</v>
       </c>
       <c r="L6" t="n">
         <v>36008.4</v>
@@ -18366,7 +18366,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>105.78</v>
       </c>
       <c r="L7" t="n">
         <v>84438</v>
@@ -18404,7 +18404,7 @@
         <v>5.95</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>116.1</v>
       </c>
       <c r="L8" t="n">
         <v>99811.8</v>
@@ -18442,7 +18442,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="L9" t="n">
         <v>134889.3</v>
@@ -18480,7 +18480,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="L10" t="n">
         <v>159826.2</v>
@@ -18518,7 +18518,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="L11" t="n">
         <v>239880</v>
@@ -18556,7 +18556,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="L12" t="n">
         <v>250110</v>
@@ -18594,7 +18594,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="L13" t="n">
         <v>201870</v>
@@ -18632,7 +18632,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="L14" t="n">
         <v>84420</v>
@@ -18670,7 +18670,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L15" t="n">
         <v>36510</v>
@@ -18708,7 +18708,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L16" t="n">
         <v>12660</v>
@@ -18746,7 +18746,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
         <v>5850</v>
@@ -18784,7 +18784,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>1980</v>
@@ -18822,7 +18822,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>720</v>
@@ -19222,7 +19222,7 @@
         <v>52499.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>752663.52</v>
       </c>
       <c r="L5" t="n">
         <v>140650.02</v>
@@ -19260,7 +19260,7 @@
         <v>58333</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1303507.4</v>
       </c>
       <c r="L6" t="n">
         <v>339199.13</v>
@@ -19298,7 +19298,7 @@
         <v>40833.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2256710.52</v>
       </c>
       <c r="L7" t="n">
         <v>795405.96</v>
@@ -19336,7 +19336,7 @@
         <v>347081.35</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2476877.4</v>
       </c>
       <c r="L8" t="n">
         <v>940227.16</v>
@@ -19374,7 +19374,7 @@
         <v>55416.35</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2858756</v>
       </c>
       <c r="L9" t="n">
         <v>1270657.21</v>
@@ -19412,7 +19412,7 @@
         <v>524997</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3541444</v>
       </c>
       <c r="L10" t="n">
         <v>1505562.8</v>
@@ -19450,7 +19450,7 @@
         <v>174999</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4288134</v>
       </c>
       <c r="L11" t="n">
         <v>2259669.6</v>
@@ -19488,7 +19488,7 @@
         <v>174999</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>4736148</v>
       </c>
       <c r="L12" t="n">
         <v>2356036.2</v>
@@ -19526,7 +19526,7 @@
         <v>291665</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>4522808</v>
       </c>
       <c r="L13" t="n">
         <v>1901615.4</v>
@@ -19564,7 +19564,7 @@
         <v>58333</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2069398</v>
       </c>
       <c r="L14" t="n">
         <v>795236.4</v>
@@ -19602,7 +19602,7 @@
         <v>174999</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>874694</v>
       </c>
       <c r="L15" t="n">
         <v>343924.2</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>234674</v>
       </c>
       <c r="L16" t="n">
         <v>119257.2</v>
@@ -19678,7 +19678,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>128004</v>
       </c>
       <c r="L17" t="n">
         <v>55107</v>
@@ -19716,7 +19716,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L18" t="n">
         <v>18651.6</v>
@@ -19754,7 +19754,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L19" t="n">
         <v>6782.4</v>
@@ -20116,7 +20116,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="L4" t="n">
         <v>307470</v>
@@ -20154,7 +20154,7 @@
         <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="L5" t="n">
         <v>339450</v>
@@ -20192,7 +20192,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="L6" t="n">
         <v>225150</v>
@@ -20230,7 +20230,7 @@
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L7" t="n">
         <v>163230</v>
@@ -20268,7 +20268,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L8" t="n">
         <v>89820</v>
@@ -20306,7 +20306,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L9" t="n">
         <v>86310</v>
@@ -20344,7 +20344,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L10" t="n">
         <v>29220</v>
@@ -21086,7 +21086,7 @@
         <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>123.48</v>
       </c>
       <c r="L5" t="n">
         <v>71284.5</v>
@@ -21124,7 +21124,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>132.6</v>
       </c>
       <c r="L6" t="n">
         <v>83305.5</v>
@@ -21162,7 +21162,7 @@
         <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>97938</v>
@@ -21200,7 +21200,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>63772.2</v>
@@ -21238,7 +21238,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L9" t="n">
         <v>69911.10000000001</v>
@@ -21276,7 +21276,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L10" t="n">
         <v>26005.8</v>
@@ -22018,7 +22018,7 @@
         <v>227498.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2634322.32</v>
       </c>
       <c r="L5" t="n">
         <v>671499.99</v>
@@ -22056,7 +22056,7 @@
         <v>116666</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2828888.4</v>
       </c>
       <c r="L6" t="n">
         <v>784737.8100000001</v>
@@ -22094,7 +22094,7 @@
         <v>244998.6</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2099265.6</v>
       </c>
       <c r="L7" t="n">
         <v>922575.96</v>
@@ -22132,7 +22132,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1459245.6</v>
       </c>
       <c r="L8" t="n">
         <v>600734.12</v>
@@ -22170,7 +22170,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1493380</v>
       </c>
       <c r="L9" t="n">
         <v>658562.5600000001</v>
@@ -22208,7 +22208,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>341344</v>
       </c>
       <c r="L10" t="n">
         <v>244974.64</v>

--- a/risk/Risk_Analysis_T3_500yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_500yrs_Future_Breaches.xlsx
@@ -549,7 +549,7 @@
         <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>1092</v>
+        <v>405</v>
       </c>
       <c r="L4" t="n">
         <v>1357260</v>
@@ -590,7 +590,7 @@
         <v>31</v>
       </c>
       <c r="K5" t="n">
-        <v>786</v>
+        <v>316</v>
       </c>
       <c r="L5" t="n">
         <v>1072590</v>
@@ -631,7 +631,7 @@
         <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>482</v>
+        <v>194</v>
       </c>
       <c r="L6" t="n">
         <v>602250</v>
@@ -672,7 +672,7 @@
         <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>381</v>
+        <v>174</v>
       </c>
       <c r="L7" t="n">
         <v>491220</v>
@@ -713,7 +713,7 @@
         <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>335</v>
+        <v>140</v>
       </c>
       <c r="L8" t="n">
         <v>410520</v>
@@ -754,7 +754,7 @@
         <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>334</v>
+        <v>137</v>
       </c>
       <c r="L9" t="n">
         <v>457500</v>
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>409</v>
+        <v>138</v>
       </c>
       <c r="L10" t="n">
         <v>446370</v>
@@ -836,7 +836,7 @@
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>354</v>
+        <v>107</v>
       </c>
       <c r="L11" t="n">
         <v>422010</v>
@@ -877,7 +877,7 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>343</v>
+        <v>109</v>
       </c>
       <c r="L12" t="n">
         <v>386640</v>
@@ -918,7 +918,7 @@
         <v>9</v>
       </c>
       <c r="K13" t="n">
-        <v>286</v>
+        <v>67</v>
       </c>
       <c r="L13" t="n">
         <v>292260</v>
@@ -959,7 +959,7 @@
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>135</v>
+        <v>17</v>
       </c>
       <c r="L14" t="n">
         <v>167730</v>
@@ -1000,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
         <v>134370</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>70650</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>33180</v>
@@ -1123,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>14130</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>5400</v>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>4260</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>14100</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>13710</v>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>15510</v>
@@ -1676,7 +1676,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>14520</v>
@@ -1717,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>16050</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
         <v>20850</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
         <v>28260</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L11" t="n">
         <v>39180</v>
@@ -1881,7 +1881,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>46530</v>
@@ -1922,7 +1922,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
         <v>43500</v>
@@ -1963,7 +1963,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>70320</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
         <v>92850</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>55080</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>26550</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>11370</v>
@@ -2168,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>4380</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>3360</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.98</v>
+        <v>1.99</v>
       </c>
       <c r="L5" t="n">
         <v>2879.1</v>
@@ -2639,7 +2639,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.56</v>
+        <v>3.04</v>
       </c>
       <c r="L6" t="n">
         <v>5738.7</v>
@@ -2680,7 +2680,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.83</v>
+        <v>2.55</v>
       </c>
       <c r="L7" t="n">
         <v>8712</v>
@@ -2721,7 +2721,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>8.83</v>
+        <v>2.21</v>
       </c>
       <c r="L8" t="n">
         <v>11395.5</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>13.65</v>
+        <v>6.42</v>
       </c>
       <c r="L9" t="n">
         <v>16888.5</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>14.79</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>25151.4</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>17.97</v>
+        <v>10.78</v>
       </c>
       <c r="L11" t="n">
         <v>39180</v>
@@ -2885,7 +2885,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>23.18</v>
+        <v>5.56</v>
       </c>
       <c r="L12" t="n">
         <v>46530</v>
@@ -2926,7 +2926,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>22.79</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
         <v>43500</v>
@@ -2967,7 +2967,7 @@
         <v>2</v>
       </c>
       <c r="K14" t="n">
-        <v>31.1</v>
+        <v>2.92</v>
       </c>
       <c r="L14" t="n">
         <v>70320</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>41.41</v>
+        <v>5.92</v>
       </c>
       <c r="L15" t="n">
         <v>92850</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>55080</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>26550</v>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>11370</v>
@@ -3172,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>4380</v>
@@ -3254,7 +3254,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>3360</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>144648.32</v>
+        <v>96432.22</v>
       </c>
       <c r="L5" t="n">
         <v>518238</v>
@@ -3643,7 +3643,7 @@
         <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>221561.03</v>
+        <v>147707.35</v>
       </c>
       <c r="L6" t="n">
         <v>1032966</v>
@@ -3684,7 +3684,7 @@
         <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>185872.37</v>
+        <v>123914.91</v>
       </c>
       <c r="L7" t="n">
         <v>1568160</v>
@@ -3725,7 +3725,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>428846.59</v>
+        <v>107211.65</v>
       </c>
       <c r="L8" t="n">
         <v>2051190</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>662837.96</v>
+        <v>311923.74</v>
       </c>
       <c r="L9" t="n">
         <v>3039930</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>718143.24</v>
+        <v>422437.2</v>
       </c>
       <c r="L10" t="n">
         <v>4527252</v>
@@ -3848,7 +3848,7 @@
         <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>872551.3199999999</v>
+        <v>523530.79</v>
       </c>
       <c r="L11" t="n">
         <v>7052400</v>
@@ -3889,7 +3889,7 @@
         <v>48556</v>
       </c>
       <c r="K12" t="n">
-        <v>1125285.3</v>
+        <v>270068.47</v>
       </c>
       <c r="L12" t="n">
         <v>8375400</v>
@@ -3930,7 +3930,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>1106494.13</v>
+        <v>184415.69</v>
       </c>
       <c r="L13" t="n">
         <v>7830000</v>
@@ -3971,7 +3971,7 @@
         <v>48556</v>
       </c>
       <c r="K14" t="n">
-        <v>1510285.82</v>
+        <v>141589.3</v>
       </c>
       <c r="L14" t="n">
         <v>12657600</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2010801.07</v>
+        <v>287257.3</v>
       </c>
       <c r="L15" t="n">
         <v>16713000</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1359568</v>
+        <v>194224</v>
       </c>
       <c r="L16" t="n">
         <v>9914400</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>582672</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>4779000</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>437004</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>2046600</v>
@@ -4176,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>788400</v>
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>604800</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="L4" t="n">
         <v>184920</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
         <v>106740</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
         <v>28980</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>11940</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>20.52</v>
+        <v>11.25</v>
       </c>
       <c r="L5" t="n">
         <v>22415.4</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6</v>
+        <v>2.54</v>
       </c>
       <c r="L6" t="n">
         <v>10722.6</v>
@@ -5692,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
         <v>7164</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>996466.23</v>
+        <v>546449.22</v>
       </c>
       <c r="L5" t="n">
         <v>4034772</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>369268.38</v>
+        <v>123089.46</v>
       </c>
       <c r="L6" t="n">
         <v>1930068</v>
@@ -6696,7 +6696,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>123914.91</v>
+        <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
         <v>1289520</v>
@@ -7577,7 +7577,7 @@
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>236</v>
+        <v>47</v>
       </c>
       <c r="L4" t="n">
         <v>191280</v>
@@ -7618,7 +7618,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
         <v>102090</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>31470</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>7470</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>3990</v>
@@ -8622,7 +8622,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>41.04</v>
+        <v>7.94</v>
       </c>
       <c r="L5" t="n">
         <v>21438.9</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>16.73</v>
+        <v>3.04</v>
       </c>
       <c r="L6" t="n">
         <v>11643.9</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4482</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2832.9</v>
@@ -9626,7 +9626,7 @@
         <v>58267.2</v>
       </c>
       <c r="K5" t="n">
-        <v>1992932.46</v>
+        <v>385728.86</v>
       </c>
       <c r="L5" t="n">
         <v>3859002</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>812390.4399999999</v>
+        <v>147707.35</v>
       </c>
       <c r="L6" t="n">
         <v>2095902</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>154893.64</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>806760</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>142948.86</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>509922</v>
@@ -10589,7 +10589,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>164</v>
+        <v>96</v>
       </c>
       <c r="L4" t="n">
         <v>134310</v>
@@ -10630,7 +10630,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="L5" t="n">
         <v>133020</v>
@@ -10671,7 +10671,7 @@
         <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="L6" t="n">
         <v>107310</v>
@@ -10712,7 +10712,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="L7" t="n">
         <v>102090</v>
@@ -10753,7 +10753,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="L8" t="n">
         <v>109290</v>
@@ -10794,7 +10794,7 @@
         <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="L9" t="n">
         <v>144810</v>
@@ -10835,7 +10835,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="L10" t="n">
         <v>186720</v>
@@ -10876,7 +10876,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="L11" t="n">
         <v>129630</v>
@@ -10917,7 +10917,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="L12" t="n">
         <v>77070</v>
@@ -10958,7 +10958,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
         <v>42060</v>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>11760</v>
@@ -11286,7 +11286,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>630</v>
@@ -11634,7 +11634,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>260.17</v>
+        <v>104.6</v>
       </c>
       <c r="L5" t="n">
         <v>225243.9</v>
@@ -11675,7 +11675,7 @@
         <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>244.37</v>
+        <v>98.36</v>
       </c>
       <c r="L6" t="n">
         <v>222832.5</v>
@@ -11716,7 +11716,7 @@
         <v>9.1</v>
       </c>
       <c r="K7" t="n">
-        <v>243.08</v>
+        <v>111.01</v>
       </c>
       <c r="L7" t="n">
         <v>294732</v>
@@ -11757,7 +11757,7 @@
         <v>11.05</v>
       </c>
       <c r="K8" t="n">
-        <v>246.56</v>
+        <v>103.04</v>
       </c>
       <c r="L8" t="n">
         <v>291469.2</v>
@@ -11798,7 +11798,7 @@
         <v>9.5</v>
       </c>
       <c r="K9" t="n">
-        <v>268.2</v>
+        <v>110.01</v>
       </c>
       <c r="L9" t="n">
         <v>370575</v>
@@ -11839,7 +11839,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>355.83</v>
+        <v>120.06</v>
       </c>
       <c r="L10" t="n">
         <v>397269.3</v>
@@ -11880,7 +11880,7 @@
         <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>318.07</v>
+        <v>96.14</v>
       </c>
       <c r="L11" t="n">
         <v>422010</v>
@@ -11921,7 +11921,7 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>317.96</v>
+        <v>101.04</v>
       </c>
       <c r="L12" t="n">
         <v>386640</v>
@@ -11962,7 +11962,7 @@
         <v>9</v>
       </c>
       <c r="K13" t="n">
-        <v>271.56</v>
+        <v>63.62</v>
       </c>
       <c r="L13" t="n">
         <v>292260</v>
@@ -12003,7 +12003,7 @@
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>131.22</v>
+        <v>16.52</v>
       </c>
       <c r="L14" t="n">
         <v>167730</v>
@@ -12044,7 +12044,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>84.8</v>
+        <v>10.85</v>
       </c>
       <c r="L15" t="n">
         <v>134370</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>70650</v>
@@ -12126,7 +12126,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>33180</v>
@@ -12167,7 +12167,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>14130</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>5400</v>
@@ -12290,7 +12290,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>4260</v>
@@ -12638,7 +12638,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>55.94</v>
+        <v>34.09</v>
       </c>
       <c r="L5" t="n">
         <v>27934.2</v>
@@ -12679,7 +12679,7 @@
         <v>6.5</v>
       </c>
       <c r="K6" t="n">
-        <v>65.91</v>
+        <v>37.01</v>
       </c>
       <c r="L6" t="n">
         <v>39704.7</v>
@@ -12720,7 +12720,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>79.75</v>
+        <v>44.02</v>
       </c>
       <c r="L7" t="n">
         <v>61254</v>
@@ -12761,7 +12761,7 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>92</v>
+        <v>47.1</v>
       </c>
       <c r="L8" t="n">
         <v>77595.89999999999</v>
@@ -12802,7 +12802,7 @@
         <v>5.7</v>
       </c>
       <c r="K9" t="n">
-        <v>93.15000000000001</v>
+        <v>46.57</v>
       </c>
       <c r="L9" t="n">
         <v>117296.1</v>
@@ -12843,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>180.09</v>
+        <v>68.73</v>
       </c>
       <c r="L10" t="n">
         <v>166180.8</v>
@@ -12884,7 +12884,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>118.6</v>
+        <v>40.43</v>
       </c>
       <c r="L11" t="n">
         <v>129630</v>
@@ -12925,7 +12925,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>88.98999999999999</v>
+        <v>30.59</v>
       </c>
       <c r="L12" t="n">
         <v>77070</v>
@@ -12966,7 +12966,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>47.48</v>
+        <v>6.65</v>
       </c>
       <c r="L13" t="n">
         <v>42060</v>
@@ -13007,7 +13007,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>5.83</v>
+        <v>1.94</v>
       </c>
       <c r="L14" t="n">
         <v>11760</v>
@@ -13294,7 +13294,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>630</v>
@@ -13642,7 +13642,7 @@
         <v>21850.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2716174.08</v>
+        <v>1655419.71</v>
       </c>
       <c r="L5" t="n">
         <v>5028156</v>
@@ -13683,7 +13683,7 @@
         <v>157807</v>
       </c>
       <c r="K6" t="n">
-        <v>3200325.96</v>
+        <v>1797106.12</v>
       </c>
       <c r="L6" t="n">
         <v>7146846</v>
@@ -13724,7 +13724,7 @@
         <v>67978.39999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>3872341</v>
+        <v>2137532.23</v>
       </c>
       <c r="L7" t="n">
         <v>11025720</v>
@@ -13765,7 +13765,7 @@
         <v>61908.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4467152</v>
+        <v>2287181.82</v>
       </c>
       <c r="L8" t="n">
         <v>13967262</v>
@@ -13806,7 +13806,7 @@
         <v>138384.6</v>
       </c>
       <c r="K9" t="n">
-        <v>4522894.29</v>
+        <v>2261447.14</v>
       </c>
       <c r="L9" t="n">
         <v>21113298</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>8744450.039999999</v>
+        <v>3337253.88</v>
       </c>
       <c r="L10" t="n">
         <v>29912544</v>
@@ -13888,7 +13888,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>5758838.71</v>
+        <v>1963240.47</v>
       </c>
       <c r="L11" t="n">
         <v>23333400</v>
@@ -13929,7 +13929,7 @@
         <v>48556</v>
       </c>
       <c r="K12" t="n">
-        <v>4321095.55</v>
+        <v>1485376.6</v>
       </c>
       <c r="L12" t="n">
         <v>13872600</v>
@@ -13970,7 +13970,7 @@
         <v>24278</v>
       </c>
       <c r="K13" t="n">
-        <v>2305196.1</v>
+        <v>322727.45</v>
       </c>
       <c r="L13" t="n">
         <v>7570800</v>
@@ -14011,7 +14011,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>283178.59</v>
+        <v>94392.86</v>
       </c>
       <c r="L14" t="n">
         <v>2116800</v>
@@ -14298,7 +14298,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>113400</v>
@@ -14605,7 +14605,7 @@
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="L4" t="n">
         <v>438930</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
         <v>249270</v>
@@ -14687,7 +14687,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>42870</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>23.5</v>
+        <v>10.59</v>
       </c>
       <c r="L5" t="n">
         <v>52346.7</v>
@@ -15691,7 +15691,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>15861.9</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1141114.56</v>
+        <v>514305.15</v>
       </c>
       <c r="L5" t="n">
         <v>9422406</v>
@@ -16695,7 +16695,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>147707.35</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2855142</v>
@@ -17658,7 +17658,7 @@
         <v>225785.4</v>
       </c>
       <c r="K5" t="n">
-        <v>12632620.3</v>
+        <v>5078763.38</v>
       </c>
       <c r="L5" t="n">
         <v>40543902</v>
@@ -17699,7 +17699,7 @@
         <v>267058</v>
       </c>
       <c r="K6" t="n">
-        <v>11865823.94</v>
+        <v>4775871.05</v>
       </c>
       <c r="L6" t="n">
         <v>40109850</v>
@@ -17740,7 +17740,7 @@
         <v>220929.8</v>
       </c>
       <c r="K7" t="n">
-        <v>11802895.37</v>
+        <v>5390298.67</v>
       </c>
       <c r="L7" t="n">
         <v>53051760</v>
@@ -17781,7 +17781,7 @@
         <v>268271.9</v>
       </c>
       <c r="K8" t="n">
-        <v>11971967.36</v>
+        <v>5003210.24</v>
       </c>
       <c r="L8" t="n">
         <v>52464456</v>
@@ -17822,7 +17822,7 @@
         <v>230641</v>
       </c>
       <c r="K9" t="n">
-        <v>13022816.31</v>
+        <v>5341694.12</v>
       </c>
       <c r="L9" t="n">
         <v>66703500</v>
@@ -17863,7 +17863,7 @@
         <v>218502</v>
       </c>
       <c r="K10" t="n">
-        <v>17277681.48</v>
+        <v>5829633.36</v>
       </c>
       <c r="L10" t="n">
         <v>71508474</v>
@@ -17904,7 +17904,7 @@
         <v>145668</v>
       </c>
       <c r="K11" t="n">
-        <v>15444158.36</v>
+        <v>4668149.56</v>
       </c>
       <c r="L11" t="n">
         <v>75961800</v>
@@ -17945,7 +17945,7 @@
         <v>169946</v>
       </c>
       <c r="K12" t="n">
-        <v>15438914.32</v>
+        <v>4906243.91</v>
       </c>
       <c r="L12" t="n">
         <v>69595200</v>
@@ -17986,7 +17986,7 @@
         <v>218502</v>
       </c>
       <c r="K13" t="n">
-        <v>13185721.69</v>
+        <v>3088962.77</v>
       </c>
       <c r="L13" t="n">
         <v>52606800</v>
@@ -18027,7 +18027,7 @@
         <v>72834</v>
       </c>
       <c r="K14" t="n">
-        <v>6371518.32</v>
+        <v>802339.34</v>
       </c>
       <c r="L14" t="n">
         <v>30191400</v>
@@ -18068,7 +18068,7 @@
         <v>72834</v>
       </c>
       <c r="K15" t="n">
-        <v>4117354.58</v>
+        <v>526638.38</v>
       </c>
       <c r="L15" t="n">
         <v>24186600</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1893684</v>
+        <v>194224</v>
       </c>
       <c r="L16" t="n">
         <v>12717000</v>
@@ -18150,7 +18150,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>874008</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>5972400</v>
@@ -18191,7 +18191,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>485560</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>2543400</v>
@@ -18232,7 +18232,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>972000</v>
@@ -18314,7 +18314,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>766800</v>
@@ -18621,7 +18621,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
         <v>52980</v>
@@ -18662,7 +18662,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
         <v>69510</v>
@@ -18703,7 +18703,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="L6" t="n">
         <v>96720</v>
@@ -18744,7 +18744,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="L7" t="n">
         <v>139920</v>
@@ -18785,7 +18785,7 @@
         <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
         <v>139860</v>
@@ -18826,7 +18826,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="L9" t="n">
         <v>166350</v>
@@ -18867,7 +18867,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>166</v>
+        <v>47</v>
       </c>
       <c r="L10" t="n">
         <v>179640</v>
@@ -18908,7 +18908,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>201</v>
+        <v>50</v>
       </c>
       <c r="L11" t="n">
         <v>239640</v>
@@ -18949,7 +18949,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>222</v>
+        <v>70</v>
       </c>
       <c r="L12" t="n">
         <v>249960</v>
@@ -18990,7 +18990,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>212</v>
+        <v>56</v>
       </c>
       <c r="L13" t="n">
         <v>201960</v>
@@ -19031,7 +19031,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
         <v>84450</v>
@@ -19072,7 +19072,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>36600</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>12660</v>
@@ -19154,7 +19154,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>5850</v>
@@ -19195,7 +19195,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>1980</v>
@@ -19236,7 +19236,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>720</v>
@@ -19666,7 +19666,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>18.54</v>
+        <v>12.58</v>
       </c>
       <c r="L5" t="n">
         <v>14597.1</v>
@@ -19707,7 +19707,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>43.1</v>
+        <v>27.38</v>
       </c>
       <c r="L6" t="n">
         <v>35786.4</v>
@@ -19748,7 +19748,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>76.56</v>
+        <v>38.92</v>
       </c>
       <c r="L7" t="n">
         <v>83952</v>
@@ -19789,7 +19789,7 @@
         <v>5.95</v>
       </c>
       <c r="K8" t="n">
-        <v>84.64</v>
+        <v>36.8</v>
       </c>
       <c r="L8" t="n">
         <v>99300.60000000001</v>
@@ -19830,7 +19830,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>105.19</v>
+        <v>47.38</v>
       </c>
       <c r="L9" t="n">
         <v>134743.5</v>
@@ -19871,7 +19871,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>144.42</v>
+        <v>40.89</v>
       </c>
       <c r="L10" t="n">
         <v>159879.6</v>
@@ -19912,7 +19912,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>180.6</v>
+        <v>44.92</v>
       </c>
       <c r="L11" t="n">
         <v>239640</v>
@@ -19953,7 +19953,7 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>205.79</v>
+        <v>64.89</v>
       </c>
       <c r="L12" t="n">
         <v>249960</v>
@@ -19994,7 +19994,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>201.29</v>
+        <v>53.17</v>
       </c>
       <c r="L13" t="n">
         <v>201960</v>
@@ -20035,7 +20035,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>94.28</v>
+        <v>11.66</v>
       </c>
       <c r="L14" t="n">
         <v>84450</v>
@@ -20076,7 +20076,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>41.41</v>
+        <v>2.96</v>
       </c>
       <c r="L15" t="n">
         <v>36600</v>
@@ -20117,7 +20117,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>12660</v>
@@ -20158,7 +20158,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>5850</v>
@@ -20199,7 +20199,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>1980</v>
@@ -20240,7 +20240,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>720</v>
@@ -20670,7 +20670,7 @@
         <v>21850.2</v>
       </c>
       <c r="K5" t="n">
-        <v>900034.02</v>
+        <v>610737.37</v>
       </c>
       <c r="L5" t="n">
         <v>2627478</v>
@@ -20711,7 +20711,7 @@
         <v>24278</v>
       </c>
       <c r="K6" t="n">
-        <v>2092520.82</v>
+        <v>1329366.17</v>
       </c>
       <c r="L6" t="n">
         <v>6441552</v>
@@ -20752,7 +20752,7 @@
         <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3717447.36</v>
+        <v>1889702.41</v>
       </c>
       <c r="L7" t="n">
         <v>15111360</v>
@@ -20793,7 +20793,7 @@
         <v>144454.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4109779.84</v>
+        <v>1786860.8</v>
       </c>
       <c r="L8" t="n">
         <v>17874108</v>
@@ -20834,7 +20834,7 @@
         <v>23064.1</v>
       </c>
       <c r="K9" t="n">
-        <v>5107751.31</v>
+        <v>2300437.61</v>
       </c>
       <c r="L9" t="n">
         <v>24253830</v>
@@ -20875,7 +20875,7 @@
         <v>218502</v>
       </c>
       <c r="K10" t="n">
-        <v>7012457.52</v>
+        <v>1985454.84</v>
       </c>
       <c r="L10" t="n">
         <v>28778328</v>
@@ -20916,7 +20916,7 @@
         <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>8769140.77</v>
+        <v>2181378.3</v>
       </c>
       <c r="L11" t="n">
         <v>43135200</v>
@@ -20957,7 +20957,7 @@
         <v>72834</v>
       </c>
       <c r="K12" t="n">
-        <v>9992533.460000001</v>
+        <v>3150798.84</v>
       </c>
       <c r="L12" t="n">
         <v>44992800</v>
@@ -20998,7 +20998,7 @@
         <v>121390</v>
       </c>
       <c r="K13" t="n">
-        <v>9774031.460000001</v>
+        <v>2581819.63</v>
       </c>
       <c r="L13" t="n">
         <v>36352800</v>
@@ -21039,7 +21039,7 @@
         <v>24278</v>
       </c>
       <c r="K14" t="n">
-        <v>4578053.9</v>
+        <v>566357.1800000001</v>
       </c>
       <c r="L14" t="n">
         <v>15201000</v>
@@ -21080,7 +21080,7 @@
         <v>72834</v>
       </c>
       <c r="K15" t="n">
-        <v>2010801.07</v>
+        <v>143628.65</v>
       </c>
       <c r="L15" t="n">
         <v>6588000</v>
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>534116</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2278800</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>291336</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1053000</v>
@@ -21203,7 +21203,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>356400</v>
@@ -21244,7 +21244,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>129600</v>
@@ -21633,7 +21633,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>341</v>
+        <v>104</v>
       </c>
       <c r="L4" t="n">
         <v>307950</v>
@@ -21674,7 +21674,7 @@
         <v>13</v>
       </c>
       <c r="K5" t="n">
-        <v>295</v>
+        <v>79</v>
       </c>
       <c r="L5" t="n">
         <v>337440</v>
@@ -21715,7 +21715,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>204</v>
+        <v>50</v>
       </c>
       <c r="L6" t="n">
         <v>225210</v>
@@ -21756,7 +21756,7 @@
         <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="L7" t="n">
         <v>162870</v>
@@ -21797,7 +21797,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="L8" t="n">
         <v>90180</v>
@@ -21838,7 +21838,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="L9" t="n">
         <v>86400</v>
@@ -21879,7 +21879,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>29220</v>
@@ -22678,7 +22678,7 @@
         <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>97.65000000000001</v>
+        <v>26.15</v>
       </c>
       <c r="L5" t="n">
         <v>70862.39999999999</v>
@@ -22719,7 +22719,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>103.43</v>
+        <v>25.35</v>
       </c>
       <c r="L6" t="n">
         <v>83327.7</v>
@@ -22760,7 +22760,7 @@
         <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>76.56</v>
+        <v>23.61</v>
       </c>
       <c r="L7" t="n">
         <v>97722</v>
@@ -22801,7 +22801,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>55.94</v>
+        <v>16.19</v>
       </c>
       <c r="L8" t="n">
         <v>64027.8</v>
@@ -22842,7 +22842,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>56.21</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>69984</v>
@@ -22883,7 +22883,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>13.92</v>
+        <v>0.87</v>
       </c>
       <c r="L10" t="n">
         <v>26005.8</v>
@@ -23682,7 +23682,7 @@
         <v>94684.2</v>
       </c>
       <c r="K5" t="n">
-        <v>4741250.62</v>
+        <v>1269690.84</v>
       </c>
       <c r="L5" t="n">
         <v>12755232</v>
@@ -23723,7 +23723,7 @@
         <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>5022049.97</v>
+        <v>1230894.6</v>
       </c>
       <c r="L6" t="n">
         <v>14998986</v>
@@ -23764,7 +23764,7 @@
         <v>101967.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3717447.36</v>
+        <v>1146212.94</v>
       </c>
       <c r="L7" t="n">
         <v>17589960</v>
@@ -23805,7 +23805,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2716028.42</v>
+        <v>786218.75</v>
       </c>
       <c r="L8" t="n">
         <v>11525004</v>
@@ -23846,7 +23846,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>2729332.76</v>
+        <v>467885.62</v>
       </c>
       <c r="L9" t="n">
         <v>12597120</v>
@@ -23887,7 +23887,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>675899.52</v>
+        <v>42243.72</v>
       </c>
       <c r="L10" t="n">
         <v>4681044</v>
